--- a/research/traditional_assets/database/data/south_korea/south_korea_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_banks_regional.xlsx
@@ -588,10 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0374</v>
+        <v>0.073</v>
       </c>
       <c r="E2">
-        <v>0.114</v>
+        <v>0.07780000000000001</v>
+      </c>
+      <c r="F2">
+        <v>0.01645</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>1103.6</v>
+        <v>883.9400000000001</v>
       </c>
       <c r="L2">
-        <v>0.1707249156894898</v>
+        <v>0.1492133693450372</v>
       </c>
       <c r="M2">
-        <v>146.4439</v>
+        <v>202.9979</v>
       </c>
       <c r="N2">
-        <v>0.0386670979325641</v>
+        <v>0.07063253305497563</v>
       </c>
       <c r="O2">
-        <v>0.1326965386009424</v>
+        <v>0.2296512206710862</v>
       </c>
       <c r="P2">
-        <v>146.4439</v>
+        <v>202.9979</v>
       </c>
       <c r="Q2">
-        <v>0.0386670979325641</v>
+        <v>0.07063253305497563</v>
       </c>
       <c r="R2">
-        <v>0.1326965386009424</v>
+        <v>0.2296512206710862</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3816.6</v>
+        <v>6372.400000000001</v>
       </c>
       <c r="V2">
-        <v>1.007736382119188</v>
+        <v>2.217258176757133</v>
       </c>
       <c r="W2">
-        <v>0.09175785797438883</v>
+        <v>0.06712325798131732</v>
       </c>
       <c r="X2">
-        <v>0.2259458386742054</v>
+        <v>0.2388462015097556</v>
       </c>
       <c r="Y2">
-        <v>-0.1341879806998166</v>
+        <v>-0.1717229435284382</v>
       </c>
       <c r="Z2">
-        <v>0.1453334652325624</v>
+        <v>0.1286430589425819</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04335857385162248</v>
+        <v>0.05882651488959385</v>
       </c>
       <c r="AC2">
-        <v>-0.04335857385162248</v>
+        <v>-0.05882651488959385</v>
       </c>
       <c r="AD2">
-        <v>37029</v>
+        <v>34965.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>37029</v>
+        <v>34965.1</v>
       </c>
       <c r="AG2">
-        <v>33212.4</v>
+        <v>28592.7</v>
       </c>
       <c r="AH2">
-        <v>0.9072110896872082</v>
+        <v>0.9240468192953849</v>
       </c>
       <c r="AI2">
-        <v>0.7201451609139069</v>
+        <v>0.7423651156273089</v>
       </c>
       <c r="AJ2">
-        <v>0.897639710592248</v>
+        <v>0.9086653509900943</v>
       </c>
       <c r="AK2">
-        <v>0.6977072488246341</v>
+        <v>0.702054155453849</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0738</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="E3">
-        <v>0.119</v>
+        <v>0.07780000000000001</v>
+      </c>
+      <c r="F3">
+        <v>0.0217</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>394.1</v>
+        <v>309.7</v>
       </c>
       <c r="L3">
-        <v>0.1393416539971007</v>
+        <v>0.1271294281843931</v>
       </c>
       <c r="M3">
-        <v>55.803</v>
+        <v>74.2349</v>
       </c>
       <c r="N3">
-        <v>0.04187213926615142</v>
+        <v>0.07937863558597091</v>
       </c>
       <c r="O3">
-        <v>0.1415960416138036</v>
+        <v>0.2396993865030675</v>
       </c>
       <c r="P3">
-        <v>55.803</v>
+        <v>74.2349</v>
       </c>
       <c r="Q3">
-        <v>0.04187213926615142</v>
+        <v>0.07937863558597091</v>
       </c>
       <c r="R3">
-        <v>0.1415960416138036</v>
+        <v>0.2396993865030675</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2168.5</v>
+        <v>2629.9</v>
       </c>
       <c r="V3">
-        <v>1.627147895250244</v>
+        <v>2.812125748502994</v>
       </c>
       <c r="W3">
-        <v>0.09175785797438883</v>
+        <v>0.06712325798131732</v>
       </c>
       <c r="X3">
-        <v>0.3512169356322573</v>
+        <v>0.4299312924296601</v>
       </c>
       <c r="Y3">
-        <v>-0.2594590776578685</v>
+        <v>-0.3628080344483428</v>
       </c>
       <c r="Z3">
-        <v>0.1279831666591249</v>
+        <v>0.1186177412914975</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04327793606789875</v>
+        <v>0.05859566654597725</v>
       </c>
       <c r="AC3">
-        <v>-0.04327793606789875</v>
+        <v>-0.05859566654597725</v>
       </c>
       <c r="AD3">
-        <v>18157.3</v>
+        <v>18679.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>18157.3</v>
+        <v>18679.9</v>
       </c>
       <c r="AG3">
-        <v>15988.8</v>
+        <v>16050</v>
       </c>
       <c r="AH3">
-        <v>0.9316213442791175</v>
+        <v>0.9523224454629341</v>
       </c>
       <c r="AI3">
-        <v>0.7734772033107702</v>
+        <v>0.813751072737015</v>
       </c>
       <c r="AJ3">
-        <v>0.9230609358311924</v>
+        <v>0.9449403009679015</v>
       </c>
       <c r="AK3">
-        <v>0.7504224082904666</v>
+        <v>0.7896523561651924</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,10 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0374</v>
+        <v>0.073</v>
       </c>
       <c r="E4">
-        <v>0.114</v>
+        <v>0.08839999999999999</v>
+      </c>
+      <c r="F4">
+        <v>0.0112</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,28 +859,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>689.8</v>
+        <v>564.6</v>
       </c>
       <c r="L4">
-        <v>0.1960048873355497</v>
+        <v>0.1666814276857674</v>
       </c>
       <c r="M4">
-        <v>87.91240000000001</v>
+        <v>126.516</v>
       </c>
       <c r="N4">
-        <v>0.0384031102568583</v>
+        <v>0.07584437383849889</v>
       </c>
       <c r="O4">
-        <v>0.1274462162945781</v>
+        <v>0.2240807651434644</v>
       </c>
       <c r="P4">
-        <v>87.91240000000001</v>
+        <v>126.516</v>
       </c>
       <c r="Q4">
-        <v>0.0384031102568583</v>
+        <v>0.07584437383849889</v>
       </c>
       <c r="R4">
-        <v>0.1274462162945781</v>
+        <v>0.2240807651434644</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -880,55 +889,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1586.4</v>
+        <v>3695.3</v>
       </c>
       <c r="V4">
-        <v>0.6929931853922768</v>
+        <v>2.215274863617289</v>
       </c>
       <c r="W4">
-        <v>0.09246648793565683</v>
+        <v>0.0717152728381262</v>
       </c>
       <c r="X4">
-        <v>0.2259458386742054</v>
+        <v>0.2388462015097556</v>
       </c>
       <c r="Y4">
-        <v>-0.1334793507385486</v>
+        <v>-0.1671309286716293</v>
       </c>
       <c r="Z4">
-        <v>0.1629629972633441</v>
+        <v>0.137194862635026</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04335857385162248</v>
+        <v>0.05882651488959385</v>
       </c>
       <c r="AC4">
-        <v>-0.04335857385162248</v>
+        <v>-0.05882651488959385</v>
       </c>
       <c r="AD4">
-        <v>18427.3</v>
+        <v>15954.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>18427.3</v>
+        <v>15954.6</v>
       </c>
       <c r="AG4">
-        <v>16840.9</v>
+        <v>12259.3</v>
       </c>
       <c r="AH4">
-        <v>0.8894987087587188</v>
+        <v>0.9053436760541801</v>
       </c>
       <c r="AI4">
-        <v>0.6809944049018085</v>
+        <v>0.6801115146554811</v>
       </c>
       <c r="AJ4">
-        <v>0.880335178592898</v>
+        <v>0.8802289013024684</v>
       </c>
       <c r="AK4">
-        <v>0.6611274682997683</v>
+        <v>0.6203000480684089</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,10 +963,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0282</v>
+        <v>0.00778</v>
       </c>
       <c r="E5">
-        <v>0.0238</v>
+        <v>-0.148</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -972,28 +981,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>19.7</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="L5">
-        <v>0.1689536878216124</v>
+        <v>0.09582504970178927</v>
       </c>
       <c r="M5">
-        <v>2.7285</v>
+        <v>2.247</v>
       </c>
       <c r="N5">
-        <v>0.01649637243047158</v>
+        <v>0.008300701884004434</v>
       </c>
       <c r="O5">
-        <v>0.138502538071066</v>
+        <v>0.233091286307054</v>
       </c>
       <c r="P5">
-        <v>2.7285</v>
+        <v>2.247</v>
       </c>
       <c r="Q5">
-        <v>0.01649637243047158</v>
+        <v>0.008300701884004434</v>
       </c>
       <c r="R5">
-        <v>0.138502538071066</v>
+        <v>0.233091286307054</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1002,55 +1011,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>61.7</v>
+        <v>47.2</v>
       </c>
       <c r="V5">
-        <v>0.3730350665054414</v>
+        <v>0.1743627632065017</v>
       </c>
       <c r="W5">
-        <v>0.0449156406748746</v>
+        <v>0.02190411270165871</v>
       </c>
       <c r="X5">
-        <v>0.1054370398011889</v>
+        <v>0.0856936066134826</v>
       </c>
       <c r="Y5">
-        <v>-0.0605213991263143</v>
+        <v>-0.0637894939118239</v>
       </c>
       <c r="Z5">
-        <v>0.1487814214622943</v>
+        <v>0.1222654350996597</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04619025424972963</v>
+        <v>0.06374871871372578</v>
       </c>
       <c r="AC5">
-        <v>-0.04619025424972963</v>
+        <v>-0.06374871871372578</v>
       </c>
       <c r="AD5">
-        <v>444.4</v>
+        <v>330.6</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>444.4</v>
+        <v>330.6</v>
       </c>
       <c r="AG5">
-        <v>382.7</v>
+        <v>283.4</v>
       </c>
       <c r="AH5">
-        <v>0.7287635290259101</v>
+        <v>0.5498087477132879</v>
       </c>
       <c r="AI5">
-        <v>0.5024307518371961</v>
+        <v>0.4822757111597374</v>
       </c>
       <c r="AJ5">
-        <v>0.6982302499543879</v>
+        <v>0.5114600252661975</v>
       </c>
       <c r="AK5">
-        <v>0.465119105493437</v>
+        <v>0.4439918533604889</v>
       </c>
       <c r="AL5">
         <v>0</v>

--- a/research/traditional_assets/database/data/south_korea/south_korea_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_banks_regional.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,112 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.073</v>
+        <v>0.05185</v>
       </c>
       <c r="E2">
-        <v>0.07780000000000001</v>
+        <v>0.0585</v>
       </c>
       <c r="F2">
-        <v>0.01645</v>
+        <v>0.02926</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.008936543580744463</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.008863376113498803</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>-0.007703404071799294</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>-0.00660512082372243</v>
       </c>
       <c r="K2">
-        <v>883.9400000000001</v>
+        <v>811.9999999999999</v>
       </c>
       <c r="L2">
-        <v>0.1492133693450372</v>
+        <v>0.1207560638282051</v>
       </c>
       <c r="M2">
-        <v>202.9979</v>
+        <v>263.6948</v>
       </c>
       <c r="N2">
-        <v>0.07063253305497563</v>
+        <v>0.08122433389804407</v>
       </c>
       <c r="O2">
-        <v>0.2296512206710862</v>
+        <v>0.3247472906403942</v>
       </c>
       <c r="P2">
-        <v>202.9979</v>
+        <v>236.2488</v>
       </c>
       <c r="Q2">
-        <v>0.07063253305497563</v>
+        <v>0.07277030648390576</v>
       </c>
       <c r="R2">
-        <v>0.2296512206710862</v>
+        <v>0.2909467980295567</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>27.446</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.1040824468286822</v>
       </c>
       <c r="U2">
-        <v>6372.400000000001</v>
+        <v>6507.599999999999</v>
       </c>
       <c r="V2">
-        <v>2.217258176757133</v>
+        <v>2.004497150777761</v>
       </c>
       <c r="W2">
-        <v>0.06712325798131732</v>
+        <v>0.0599930325620091</v>
       </c>
       <c r="X2">
-        <v>0.2388462015097556</v>
+        <v>0.1432424921259055</v>
       </c>
       <c r="Y2">
-        <v>-0.1717229435284382</v>
+        <v>-0.08324945956389634</v>
       </c>
       <c r="Z2">
-        <v>0.1286430589425819</v>
+        <v>0.1683861791264543</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05882651488959385</v>
+        <v>0.05008174170600505</v>
       </c>
       <c r="AC2">
-        <v>-0.05882651488959385</v>
+        <v>-0.05264154812609382</v>
       </c>
       <c r="AD2">
-        <v>34965.1</v>
+        <v>36778.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>34965.1</v>
+        <v>36778.4</v>
       </c>
       <c r="AG2">
-        <v>28592.7</v>
+        <v>30270.8</v>
       </c>
       <c r="AH2">
-        <v>0.9240468192953849</v>
+        <v>0.9188879922248401</v>
       </c>
       <c r="AI2">
-        <v>0.7423651156273089</v>
+        <v>0.7255768073626168</v>
       </c>
       <c r="AJ2">
-        <v>0.9086653509900943</v>
+        <v>0.9031395726982782</v>
       </c>
       <c r="AK2">
-        <v>0.702054155453849</v>
+        <v>0.6851558026205895</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>5.94</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>5.495</v>
+      </c>
+      <c r="AN2">
+        <v>-884.0961538461538</v>
+      </c>
+      <c r="AO2">
+        <v>-8.72053872053872</v>
+      </c>
+      <c r="AP2">
+        <v>-727.6634615384615</v>
+      </c>
+      <c r="AQ2">
+        <v>-9.426751592356688</v>
       </c>
     </row>
     <row r="3">
@@ -713,13 +725,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.07400000000000001</v>
+        <v>0.0374</v>
       </c>
       <c r="E3">
-        <v>0.07780000000000001</v>
+        <v>0.0585</v>
       </c>
       <c r="F3">
-        <v>0.0217</v>
+        <v>0.0561</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +746,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>309.7</v>
+        <v>305.2</v>
       </c>
       <c r="L3">
-        <v>0.1271294281843931</v>
+        <v>0.1246222948142099</v>
       </c>
       <c r="M3">
-        <v>74.2349</v>
+        <v>95.1712</v>
       </c>
       <c r="N3">
-        <v>0.07937863558597091</v>
+        <v>0.08670845481049563</v>
       </c>
       <c r="O3">
-        <v>0.2396993865030675</v>
+        <v>0.3118322411533421</v>
       </c>
       <c r="P3">
-        <v>74.2349</v>
+        <v>80.3712</v>
       </c>
       <c r="Q3">
-        <v>0.07937863558597091</v>
+        <v>0.07322448979591838</v>
       </c>
       <c r="R3">
-        <v>0.2396993865030675</v>
+        <v>0.2633394495412844</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>14.8</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.1555092296829293</v>
       </c>
       <c r="U3">
-        <v>2629.9</v>
+        <v>2520.1</v>
       </c>
       <c r="V3">
-        <v>2.812125748502994</v>
+        <v>2.296009475218659</v>
       </c>
       <c r="W3">
-        <v>0.06712325798131732</v>
+        <v>0.08263165019629078</v>
       </c>
       <c r="X3">
-        <v>0.4299312924296601</v>
+        <v>0.2592075846892772</v>
       </c>
       <c r="Y3">
-        <v>-0.3628080344483428</v>
+        <v>-0.1765759344929864</v>
       </c>
       <c r="Z3">
-        <v>0.1186177412914975</v>
+        <v>0.1244157691526113</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05859566654597725</v>
+        <v>0.04976113952614642</v>
       </c>
       <c r="AC3">
-        <v>-0.05859566654597725</v>
+        <v>-0.04976113952614642</v>
       </c>
       <c r="AD3">
-        <v>18679.9</v>
+        <v>19244.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>18679.9</v>
+        <v>19244.8</v>
       </c>
       <c r="AG3">
-        <v>16050</v>
+        <v>16724.7</v>
       </c>
       <c r="AH3">
-        <v>0.9523224454629341</v>
+        <v>0.946043731319805</v>
       </c>
       <c r="AI3">
-        <v>0.813751072737015</v>
+        <v>0.7977648258537353</v>
       </c>
       <c r="AJ3">
-        <v>0.9449403009679015</v>
+        <v>0.9384142338530942</v>
       </c>
       <c r="AK3">
-        <v>0.7896523561651924</v>
+        <v>0.7741733901765008</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -838,13 +850,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.073</v>
+        <v>0.0663</v>
       </c>
       <c r="E4">
-        <v>0.08839999999999999</v>
+        <v>0.101</v>
       </c>
       <c r="F4">
-        <v>0.0112</v>
+        <v>0.00242</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,85 +871,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>564.6</v>
+        <v>549.3</v>
       </c>
       <c r="L4">
-        <v>0.1666814276857674</v>
+        <v>0.1576409814894533</v>
       </c>
       <c r="M4">
-        <v>126.516</v>
+        <v>161.3544</v>
       </c>
       <c r="N4">
-        <v>0.07584437383849889</v>
+        <v>0.09029850579215402</v>
       </c>
       <c r="O4">
-        <v>0.2240807651434644</v>
+        <v>0.2937454942654288</v>
       </c>
       <c r="P4">
-        <v>126.516</v>
+        <v>149.4544</v>
       </c>
       <c r="Q4">
-        <v>0.07584437383849889</v>
+        <v>0.08363892775197269</v>
       </c>
       <c r="R4">
-        <v>0.2240807651434644</v>
+        <v>0.2720815583469872</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>11.90000000000001</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.07375070032177619</v>
       </c>
       <c r="U4">
-        <v>3695.3</v>
+        <v>3418.7</v>
       </c>
       <c r="V4">
-        <v>2.215274863617289</v>
+        <v>1.913201634114947</v>
       </c>
       <c r="W4">
-        <v>0.0717152728381262</v>
+        <v>0.0802565638560554</v>
       </c>
       <c r="X4">
-        <v>0.2388462015097556</v>
+        <v>0.1604110522139013</v>
       </c>
       <c r="Y4">
-        <v>-0.1671309286716293</v>
+        <v>-0.08015448835784594</v>
       </c>
       <c r="Z4">
-        <v>0.137194862635026</v>
+        <v>0.1825884646220112</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05882651488959385</v>
+        <v>0.04998205421652842</v>
       </c>
       <c r="AC4">
-        <v>-0.05882651488959385</v>
+        <v>-0.04998205421652842</v>
       </c>
       <c r="AD4">
-        <v>15954.6</v>
+        <v>16218.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>15954.6</v>
+        <v>16218.9</v>
       </c>
       <c r="AG4">
-        <v>12259.3</v>
+        <v>12800.2</v>
       </c>
       <c r="AH4">
-        <v>0.9053436760541801</v>
+        <v>0.9007597551899944</v>
       </c>
       <c r="AI4">
-        <v>0.6801115146554811</v>
+        <v>0.6685917809574455</v>
       </c>
       <c r="AJ4">
-        <v>0.8802289013024684</v>
+        <v>0.877501353936012</v>
       </c>
       <c r="AK4">
-        <v>0.6203000480684089</v>
+        <v>0.6142248411677768</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -963,10 +975,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.00778</v>
+        <v>0.0173</v>
       </c>
       <c r="E5">
-        <v>-0.148</v>
+        <v>-0.0558</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -981,28 +993,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>9.640000000000001</v>
+        <v>14.1</v>
       </c>
       <c r="L5">
-        <v>0.09582504970178927</v>
+        <v>0.1286496350364963</v>
       </c>
       <c r="M5">
-        <v>2.247</v>
+        <v>2.3754</v>
       </c>
       <c r="N5">
-        <v>0.008300701884004434</v>
+        <v>0.01173037037037037</v>
       </c>
       <c r="O5">
-        <v>0.233091286307054</v>
+        <v>0.168468085106383</v>
       </c>
       <c r="P5">
-        <v>2.247</v>
+        <v>2.3754</v>
       </c>
       <c r="Q5">
-        <v>0.008300701884004434</v>
+        <v>0.01173037037037037</v>
       </c>
       <c r="R5">
-        <v>0.233091286307054</v>
+        <v>0.168468085106383</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1011,61 +1023,192 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>47.2</v>
+        <v>45.6</v>
       </c>
       <c r="V5">
-        <v>0.1743627632065017</v>
+        <v>0.2251851851851852</v>
       </c>
       <c r="W5">
-        <v>0.02190411270165871</v>
+        <v>0.03972950126796281</v>
       </c>
       <c r="X5">
-        <v>0.0856936066134826</v>
+        <v>0.07374870809384146</v>
       </c>
       <c r="Y5">
-        <v>-0.0637894939118239</v>
+        <v>-0.03401920682587865</v>
       </c>
       <c r="Z5">
-        <v>0.1222654350996597</v>
+        <v>0.1717060943130189</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06374871871372578</v>
+        <v>0.05530104203565922</v>
       </c>
       <c r="AC5">
-        <v>-0.06374871871372578</v>
+        <v>-0.05530104203565922</v>
       </c>
       <c r="AD5">
-        <v>330.6</v>
+        <v>335.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>330.6</v>
+        <v>335.8</v>
       </c>
       <c r="AG5">
-        <v>283.4</v>
+        <v>290.2</v>
       </c>
       <c r="AH5">
-        <v>0.5498087477132879</v>
+        <v>0.6238157161434146</v>
       </c>
       <c r="AI5">
-        <v>0.4822757111597374</v>
+        <v>0.4576178795312075</v>
       </c>
       <c r="AJ5">
-        <v>0.5114600252661975</v>
+        <v>0.588999391110209</v>
       </c>
       <c r="AK5">
-        <v>0.4439918533604889</v>
+        <v>0.4216797442603894</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sangsangin Co., Ltd. (KOSDAQ:A038540)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.151</v>
+      </c>
+      <c r="G6">
+        <v>0.08821491485613622</v>
+      </c>
+      <c r="H6">
+        <v>0.08749266001174398</v>
+      </c>
+      <c r="I6">
+        <v>-0.07604227833235466</v>
+      </c>
+      <c r="J6">
+        <v>-0.07604227833235466</v>
+      </c>
+      <c r="K6">
+        <v>-56.6</v>
+      </c>
+      <c r="L6">
+        <v>-0.0830886670581327</v>
+      </c>
+      <c r="M6">
+        <v>4.793799999999999</v>
+      </c>
+      <c r="N6">
+        <v>0.0300551724137931</v>
+      </c>
+      <c r="O6">
+        <v>-0.08469611307420492</v>
+      </c>
+      <c r="P6">
+        <v>4.0478</v>
+      </c>
+      <c r="Q6">
+        <v>0.02537805642633228</v>
+      </c>
+      <c r="R6">
+        <v>-0.07151590106007066</v>
+      </c>
+      <c r="S6">
+        <v>0.7459999999999996</v>
+      </c>
+      <c r="T6">
+        <v>0.155617672827402</v>
+      </c>
+      <c r="U6">
+        <v>523.2</v>
+      </c>
+      <c r="V6">
+        <v>3.28025078369906</v>
+      </c>
+      <c r="W6">
+        <v>-0.1049119555143651</v>
+      </c>
+      <c r="X6">
+        <v>0.1260739320379096</v>
+      </c>
+      <c r="Y6">
+        <v>-0.2309858875522747</v>
+      </c>
+      <c r="Z6">
+        <v>1.291129643669446</v>
+      </c>
+      <c r="AA6">
+        <v>-0.09818043972706593</v>
+      </c>
+      <c r="AB6">
+        <v>0.05018142919548167</v>
+      </c>
+      <c r="AC6">
+        <v>-0.1483618689225476</v>
+      </c>
+      <c r="AD6">
+        <v>978.9</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>978.9</v>
+      </c>
+      <c r="AG6">
+        <v>455.6999999999999</v>
+      </c>
+      <c r="AH6">
+        <v>0.8598910751932536</v>
+      </c>
+      <c r="AI6">
+        <v>0.6223140495867768</v>
+      </c>
+      <c r="AJ6">
+        <v>0.7407347204161248</v>
+      </c>
+      <c r="AK6">
+        <v>0.4340826824156982</v>
+      </c>
+      <c r="AL6">
+        <v>5.94</v>
+      </c>
+      <c r="AM6">
+        <v>5.495</v>
+      </c>
+      <c r="AN6">
+        <v>-23.53125</v>
+      </c>
+      <c r="AO6">
+        <v>-8.72053872053872</v>
+      </c>
+      <c r="AP6">
+        <v>-10.95432692307692</v>
+      </c>
+      <c r="AQ6">
+        <v>-9.426751592356688</v>
       </c>
     </row>
   </sheetData>
